--- a/RS4_PE_Play/Doc/유격 검사_IO List.xlsx
+++ b/RS4_PE_Play/Doc/유격 검사_IO List.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lchto\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lchto\Desktop\RS4_PE_Play\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9ACD5B2-F5FA-46EC-9CB4-688BAC94C679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA339766-E7B1-4916-9EF8-6812EC63FA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="29699" windowHeight="17937" tabRatio="550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="48">
   <si>
     <t>TITLE</t>
   </si>
@@ -189,6 +189,26 @@
   </si>
   <si>
     <t>DATE  :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPARE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OUTPUT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INPUT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOAD 하강</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOAD 상승</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -787,6 +807,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
@@ -805,18 +831,42 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="180"/>
     </xf>
@@ -826,47 +876,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="18">
@@ -1217,85 +1237,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="46"/>
+      <c r="D1" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="40"/>
     </row>
     <row r="2" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
       <c r="G2" s="37"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
       <c r="K2" s="37"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
       <c r="O2" s="37"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
       <c r="S2" s="37"/>
     </row>
     <row r="3" spans="1:19" ht="12.85" customHeight="1" thickBot="1">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="34" t="s">
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="35"/>
+      <c r="E3" s="29"/>
       <c r="F3" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="37"/>
-      <c r="H3" s="34" t="s">
+      <c r="H3" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="35"/>
+      <c r="I3" s="29"/>
       <c r="J3" s="36" t="s">
         <v>15</v>
       </c>
       <c r="K3" s="37"/>
-      <c r="L3" s="34" t="s">
+      <c r="L3" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="35"/>
+      <c r="M3" s="29"/>
       <c r="N3" s="36" t="s">
         <v>15</v>
       </c>
       <c r="O3" s="37"/>
-      <c r="P3" s="34" t="s">
+      <c r="P3" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="35"/>
+      <c r="Q3" s="29"/>
       <c r="R3" s="36" t="s">
         <v>15</v>
       </c>
@@ -1303,10 +1327,10 @@
     </row>
     <row r="4" spans="1:19" ht="12.85" customHeight="1">
       <c r="A4" s="16"/>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="28"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="11" t="s">
         <v>16</v>
       </c>
@@ -1338,8 +1362,8 @@
     </row>
     <row r="5" spans="1:19" ht="12.85" customHeight="1">
       <c r="A5" s="16"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="29"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="11" t="s">
         <v>16</v>
       </c>
@@ -1371,8 +1395,8 @@
     </row>
     <row r="6" spans="1:19" ht="12.85" customHeight="1">
       <c r="A6" s="16"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="29"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="31"/>
       <c r="D6" s="11" t="s">
         <v>16</v>
       </c>
@@ -1404,8 +1428,8 @@
     </row>
     <row r="7" spans="1:19" ht="12.85" customHeight="1">
       <c r="A7" s="16"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="29"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="11" t="s">
         <v>16</v>
       </c>
@@ -1436,9 +1460,9 @@
       <c r="S7" s="13"/>
     </row>
     <row r="8" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="29"/>
+      <c r="A8" s="45"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="11" t="s">
         <v>16</v>
       </c>
@@ -1456,7 +1480,9 @@
         <v>4</v>
       </c>
       <c r="J8" s="15"/>
-      <c r="K8" s="13"/>
+      <c r="K8" s="13" t="s">
+        <v>46</v>
+      </c>
       <c r="L8" s="11"/>
       <c r="M8" s="12"/>
       <c r="N8" s="14"/>
@@ -1467,9 +1493,9 @@
       <c r="S8" s="13"/>
     </row>
     <row r="9" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="29"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="31"/>
       <c r="D9" s="11" t="s">
         <v>16</v>
       </c>
@@ -1487,7 +1513,9 @@
         <v>5</v>
       </c>
       <c r="J9" s="15"/>
-      <c r="K9" s="13"/>
+      <c r="K9" s="13" t="s">
+        <v>47</v>
+      </c>
       <c r="L9" s="11"/>
       <c r="M9" s="12"/>
       <c r="N9" s="14"/>
@@ -1498,9 +1526,9 @@
       <c r="S9" s="13"/>
     </row>
     <row r="10" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="29"/>
+      <c r="A10" s="45"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="11" t="s">
         <v>16</v>
       </c>
@@ -1529,9 +1557,9 @@
       <c r="S10" s="18"/>
     </row>
     <row r="11" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="29"/>
+      <c r="A11" s="46"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="31"/>
       <c r="D11" s="11" t="s">
         <v>16</v>
       </c>
@@ -1560,9 +1588,9 @@
       <c r="S11" s="18"/>
     </row>
     <row r="12" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="29"/>
+      <c r="A12" s="46"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="11" t="s">
         <v>16</v>
       </c>
@@ -1591,9 +1619,9 @@
       <c r="S12" s="13"/>
     </row>
     <row r="13" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="29"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="11" t="s">
         <v>16</v>
       </c>
@@ -1622,9 +1650,9 @@
       <c r="S13" s="18"/>
     </row>
     <row r="14" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A14" s="53"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="29"/>
+      <c r="A14" s="46"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="31"/>
       <c r="D14" s="11" t="s">
         <v>16</v>
       </c>
@@ -1653,9 +1681,9 @@
       <c r="S14" s="13"/>
     </row>
     <row r="15" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A15" s="53"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="29"/>
+      <c r="A15" s="46"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="31"/>
       <c r="D15" s="11" t="s">
         <v>16</v>
       </c>
@@ -1663,7 +1691,9 @@
         <v>4</v>
       </c>
       <c r="F15" s="14"/>
-      <c r="G15" s="13"/>
+      <c r="G15" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H15" s="11" t="s">
         <v>37</v>
       </c>
@@ -1682,9 +1712,9 @@
       <c r="S15" s="13"/>
     </row>
     <row r="16" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A16" s="53"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="29"/>
+      <c r="A16" s="46"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="11" t="s">
         <v>16</v>
       </c>
@@ -1692,7 +1722,9 @@
         <v>5</v>
       </c>
       <c r="F16" s="14"/>
-      <c r="G16" s="13"/>
+      <c r="G16" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H16" s="11" t="s">
         <v>37</v>
       </c>
@@ -1711,9 +1743,9 @@
       <c r="S16" s="13"/>
     </row>
     <row r="17" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A17" s="53"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="29"/>
+      <c r="A17" s="46"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="11" t="s">
         <v>16</v>
       </c>
@@ -1721,7 +1753,9 @@
         <v>6</v>
       </c>
       <c r="F17" s="14"/>
-      <c r="G17" s="13"/>
+      <c r="G17" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H17" s="11" t="s">
         <v>37</v>
       </c>
@@ -1740,9 +1774,9 @@
       <c r="S17" s="13"/>
     </row>
     <row r="18" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A18" s="53"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="29"/>
+      <c r="A18" s="46"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="31"/>
       <c r="D18" s="11" t="s">
         <v>16</v>
       </c>
@@ -1750,7 +1784,9 @@
         <v>7</v>
       </c>
       <c r="F18" s="14"/>
-      <c r="G18" s="13"/>
+      <c r="G18" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H18" s="11" t="s">
         <v>37</v>
       </c>
@@ -1769,9 +1805,9 @@
       <c r="S18" s="13"/>
     </row>
     <row r="19" spans="1:19" ht="12.85" customHeight="1" thickBot="1">
-      <c r="A19" s="54"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="29"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="31"/>
       <c r="D19" s="19" t="s">
         <v>16</v>
       </c>
@@ -1779,7 +1815,9 @@
         <v>8</v>
       </c>
       <c r="F19" s="27"/>
-      <c r="G19" s="21"/>
+      <c r="G19" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H19" s="11" t="s">
         <v>37</v>
       </c>
@@ -1819,92 +1857,94 @@
       <c r="S20" s="24"/>
     </row>
     <row r="21" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="41"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="43"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="45"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="46"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="40"/>
     </row>
     <row r="22" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A22" s="39"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
+      <c r="A22" s="49"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
       <c r="G22" s="37"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
       <c r="K22" s="37"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="47"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
       <c r="O22" s="37"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="41"/>
+      <c r="R22" s="41"/>
       <c r="S22" s="37"/>
     </row>
     <row r="23" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A23" s="39"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="34" t="s">
+      <c r="A23" s="49"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="35"/>
+      <c r="E23" s="29"/>
       <c r="F23" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G23" s="37"/>
-      <c r="H23" s="34" t="s">
+      <c r="H23" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="35"/>
+      <c r="I23" s="29"/>
       <c r="J23" s="36" t="s">
         <v>15</v>
       </c>
       <c r="K23" s="37"/>
-      <c r="L23" s="34" t="s">
+      <c r="L23" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="M23" s="35"/>
+      <c r="M23" s="29"/>
       <c r="N23" s="36" t="s">
         <v>15</v>
       </c>
       <c r="O23" s="37"/>
-      <c r="P23" s="34" t="s">
+      <c r="P23" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="Q23" s="35"/>
+      <c r="Q23" s="29"/>
       <c r="R23" s="36" t="s">
         <v>15</v>
       </c>
       <c r="S23" s="37"/>
     </row>
     <row r="24" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A24" s="39"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
+      <c r="A24" s="49"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
       <c r="D24" s="11" t="s">
         <v>17</v>
       </c>
@@ -1929,9 +1969,9 @@
       <c r="S24" s="13"/>
     </row>
     <row r="25" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A25" s="39"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
       <c r="D25" s="11" t="s">
         <v>17</v>
       </c>
@@ -1956,9 +1996,9 @@
       <c r="S25" s="21"/>
     </row>
     <row r="26" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A26" s="39"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
       <c r="D26" s="11" t="s">
         <v>31</v>
       </c>
@@ -1983,9 +2023,9 @@
       <c r="S26" s="13"/>
     </row>
     <row r="27" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A27" s="39"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
       <c r="D27" s="11" t="s">
         <v>31</v>
       </c>
@@ -2010,9 +2050,9 @@
       <c r="S27" s="13"/>
     </row>
     <row r="28" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A28" s="39"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
       <c r="D28" s="11" t="s">
         <v>31</v>
       </c>
@@ -2037,9 +2077,9 @@
       <c r="S28" s="13"/>
     </row>
     <row r="29" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A29" s="39"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
+      <c r="A29" s="49"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="49"/>
       <c r="D29" s="11" t="s">
         <v>31</v>
       </c>
@@ -2047,7 +2087,9 @@
         <v>5</v>
       </c>
       <c r="F29" s="15"/>
-      <c r="G29" s="13"/>
+      <c r="G29" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H29" s="11"/>
       <c r="I29" s="12"/>
       <c r="J29" s="14"/>
@@ -2062,9 +2104,9 @@
       <c r="S29" s="13"/>
     </row>
     <row r="30" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A30" s="39"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39"/>
+      <c r="A30" s="49"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="49"/>
       <c r="D30" s="11" t="s">
         <v>31</v>
       </c>
@@ -2072,7 +2114,9 @@
         <v>6</v>
       </c>
       <c r="F30" s="15"/>
-      <c r="G30" s="13"/>
+      <c r="G30" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H30" s="11"/>
       <c r="I30" s="12"/>
       <c r="J30" s="14"/>
@@ -2087,9 +2131,9 @@
       <c r="S30" s="13"/>
     </row>
     <row r="31" spans="1:19" ht="12.85" customHeight="1" thickBot="1">
-      <c r="A31" s="40"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
+      <c r="A31" s="50"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
       <c r="D31" s="11" t="s">
         <v>31</v>
       </c>
@@ -2097,7 +2141,9 @@
         <v>7</v>
       </c>
       <c r="F31" s="15"/>
-      <c r="G31" s="13"/>
+      <c r="G31" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H31" s="11"/>
       <c r="I31" s="12"/>
       <c r="J31" s="14"/>
@@ -2112,13 +2158,13 @@
       <c r="S31" s="13"/>
     </row>
     <row r="32" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A32" s="38" t="s">
+      <c r="A32" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="B32" s="38" t="s">
+      <c r="B32" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="48" t="s">
         <v>12</v>
       </c>
       <c r="D32" s="11" t="s">
@@ -2128,7 +2174,9 @@
         <v>8</v>
       </c>
       <c r="F32" s="15"/>
-      <c r="G32" s="13"/>
+      <c r="G32" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H32" s="11"/>
       <c r="I32" s="12"/>
       <c r="J32" s="14"/>
@@ -2143,9 +2191,9 @@
       <c r="S32" s="13"/>
     </row>
     <row r="33" spans="1:19" ht="12.85" customHeight="1" thickBot="1">
-      <c r="A33" s="40"/>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
+      <c r="A33" s="50"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
       <c r="D33" s="11" t="s">
         <v>31</v>
       </c>
@@ -2153,7 +2201,9 @@
         <v>9</v>
       </c>
       <c r="F33" s="15"/>
-      <c r="G33" s="13"/>
+      <c r="G33" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H33" s="11"/>
       <c r="I33" s="12"/>
       <c r="J33" s="14"/>
@@ -2178,7 +2228,9 @@
         <v>10</v>
       </c>
       <c r="F34" s="15"/>
-      <c r="G34" s="13"/>
+      <c r="G34" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H34" s="11"/>
       <c r="I34" s="12"/>
       <c r="J34" s="14"/>
@@ -2203,7 +2255,9 @@
         <v>11</v>
       </c>
       <c r="F35" s="15"/>
-      <c r="G35" s="13"/>
+      <c r="G35" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H35" s="11"/>
       <c r="I35" s="12"/>
       <c r="J35" s="14"/>
@@ -2228,7 +2282,9 @@
         <v>12</v>
       </c>
       <c r="F36" s="15"/>
-      <c r="G36" s="26"/>
+      <c r="G36" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H36" s="11"/>
       <c r="I36" s="12"/>
       <c r="J36" s="14"/>
@@ -2253,7 +2309,9 @@
         <v>13</v>
       </c>
       <c r="F37" s="15"/>
-      <c r="G37" s="26"/>
+      <c r="G37" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H37" s="11"/>
       <c r="I37" s="12"/>
       <c r="J37" s="14"/>
@@ -2278,7 +2336,9 @@
         <v>14</v>
       </c>
       <c r="F38" s="15"/>
-      <c r="G38" s="26"/>
+      <c r="G38" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
       <c r="J38" s="14"/>
@@ -2303,7 +2363,9 @@
         <v>15</v>
       </c>
       <c r="F39" s="27"/>
-      <c r="G39" s="26"/>
+      <c r="G39" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H39" s="19"/>
       <c r="I39" s="20"/>
       <c r="J39" s="27"/>
@@ -2318,9 +2380,9 @@
       <c r="S39" s="13"/>
     </row>
     <row r="40" spans="1:19" ht="12.85" customHeight="1">
-      <c r="A40" s="48"/>
-      <c r="B40" s="48"/>
-      <c r="C40" s="48"/>
+      <c r="A40" s="53"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
       <c r="D40" s="6"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
@@ -2339,9 +2401,9 @@
       <c r="S40" s="25"/>
     </row>
     <row r="41" spans="1:19" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A41" s="49"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="49"/>
+      <c r="A41" s="54"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
       <c r="D41" s="8" t="s">
         <v>13</v>
       </c>
@@ -2379,28 +2441,23 @@
     <mergeCell ref="P22:S22"/>
     <mergeCell ref="C32:C33"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="B4:B19"/>
-    <mergeCell ref="C4:C19"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A19"/>
     <mergeCell ref="A21:A31"/>
     <mergeCell ref="B21:B31"/>
     <mergeCell ref="C21:C31"/>
+    <mergeCell ref="B4:B19"/>
+    <mergeCell ref="C4:C19"/>
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="D21:G21"/>
     <mergeCell ref="H21:K21"/>
     <mergeCell ref="L21:O21"/>
     <mergeCell ref="L1:O1"/>
-    <mergeCell ref="P1:S1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:S2"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="N3:O3"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="J23:K23"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:B3"/>
@@ -2411,6 +2468,11 @@
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.24" right="0.24" top="0.79" bottom="0.28000000000000003" header="0.35" footer="0.24"/>
